--- a/property_excel/tepmpale_gnkt_osv_grp.xlsx
+++ b/property_excel/tepmpale_gnkt_osv_grp.xlsx
@@ -2523,12 +2523,6 @@
     <xf numFmtId="190" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="190" fontId="44" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="44" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="189" fontId="11" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2565,9 +2559,6 @@
     <xf numFmtId="190" fontId="44" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="190" fontId="44" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2647,12 +2638,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="190" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="190" fontId="6" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2831,71 +2816,125 @@
     <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="184" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="191" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="191" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="6" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="46" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="46" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="46" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="46" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="31" fillId="0" borderId="36" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="31" fillId="0" borderId="9" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="179" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2903,113 +2942,401 @@
     <xf numFmtId="179" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="192" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="192" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="192" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="31" fillId="0" borderId="48" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="31" fillId="0" borderId="15" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="46" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="46" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="11" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="184" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="184" fontId="11" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="191" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="191" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="6" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="6" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="6" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="31" fillId="0" borderId="15" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="31" fillId="0" borderId="36" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="31" fillId="0" borderId="9" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="172" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="185" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="185" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="186" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="46" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="46" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="190" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="190" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="190" fontId="6" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="190" fontId="6" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="190" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="190" fontId="6" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="184" fontId="11" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3026,346 +3353,19 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="46" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="46" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="39" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="187" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="392" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="6" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="46" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="46" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="43" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="43" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="43" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="43" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="43" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4245,8 +4245,8 @@
     <col min="3" max="3" width="1.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="2.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="2.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.42578125" style="47" customWidth="1"/>
-    <col min="7" max="7" width="5.140625" style="47" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" style="44" customWidth="1"/>
+    <col min="7" max="7" width="5.140625" style="44" customWidth="1"/>
     <col min="8" max="8" width="3" style="1" customWidth="1"/>
     <col min="9" max="9" width="2.85546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="3.5703125" style="1" customWidth="1"/>
@@ -4280,10 +4280,10 @@
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
-      <c r="R1" s="241"/>
-      <c r="S1" s="241"/>
-      <c r="T1" s="241"/>
-      <c r="U1" s="241"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
       <c r="V1" s="15"/>
       <c r="W1" s="15"/>
     </row>
@@ -4312,28 +4312,28 @@
       <c r="W2" s="4"/>
     </row>
     <row r="3" spans="2:24" ht="18" x14ac:dyDescent="0.25">
-      <c r="B3" s="263" t="s">
+      <c r="B3" s="229" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="263"/>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="263"/>
-      <c r="I3" s="263"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
-      <c r="M3" s="263"/>
-      <c r="N3" s="263"/>
-      <c r="O3" s="263"/>
-      <c r="P3" s="263"/>
-      <c r="Q3" s="263"/>
-      <c r="R3" s="263"/>
-      <c r="S3" s="263"/>
-      <c r="T3" s="263"/>
-      <c r="U3" s="263"/>
+      <c r="C3" s="229"/>
+      <c r="D3" s="229"/>
+      <c r="E3" s="229"/>
+      <c r="F3" s="229"/>
+      <c r="G3" s="229"/>
+      <c r="H3" s="229"/>
+      <c r="I3" s="229"/>
+      <c r="J3" s="229"/>
+      <c r="K3" s="229"/>
+      <c r="L3" s="229"/>
+      <c r="M3" s="229"/>
+      <c r="N3" s="229"/>
+      <c r="O3" s="229"/>
+      <c r="P3" s="229"/>
+      <c r="Q3" s="229"/>
+      <c r="R3" s="229"/>
+      <c r="S3" s="229"/>
+      <c r="T3" s="229"/>
+      <c r="U3" s="229"/>
       <c r="V3" s="14"/>
       <c r="W3" s="14"/>
     </row>
@@ -4349,19 +4349,19 @@
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
       <c r="L4" s="5"/>
-      <c r="M4" s="242" t="s">
+      <c r="M4" s="206" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="242"/>
-      <c r="O4" s="242"/>
-      <c r="P4" s="242"/>
-      <c r="Q4" s="242"/>
-      <c r="R4" s="242"/>
-      <c r="S4" s="242"/>
-      <c r="T4" s="242"/>
-      <c r="U4" s="242"/>
-      <c r="V4" s="242"/>
-      <c r="W4" s="242"/>
+      <c r="N4" s="206"/>
+      <c r="O4" s="206"/>
+      <c r="P4" s="206"/>
+      <c r="Q4" s="206"/>
+      <c r="R4" s="206"/>
+      <c r="S4" s="206"/>
+      <c r="T4" s="206"/>
+      <c r="U4" s="206"/>
+      <c r="V4" s="206"/>
+      <c r="W4" s="206"/>
     </row>
     <row r="5" spans="2:24" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
@@ -4375,366 +4375,366 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="13"/>
-      <c r="M5" s="243"/>
-      <c r="N5" s="243"/>
-      <c r="O5" s="243"/>
-      <c r="P5" s="243"/>
-      <c r="Q5" s="243"/>
-      <c r="R5" s="243"/>
-      <c r="S5" s="243"/>
-      <c r="T5" s="243"/>
-      <c r="U5" s="243"/>
-      <c r="V5" s="243"/>
-      <c r="W5" s="243"/>
+      <c r="M5" s="207"/>
+      <c r="N5" s="207"/>
+      <c r="O5" s="207"/>
+      <c r="P5" s="207"/>
+      <c r="Q5" s="207"/>
+      <c r="R5" s="207"/>
+      <c r="S5" s="207"/>
+      <c r="T5" s="207"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="207"/>
+      <c r="W5" s="207"/>
     </row>
     <row r="6" spans="2:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="272"/>
-      <c r="E6" s="273"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="248" t="s">
+      <c r="D6" s="169"/>
+      <c r="E6" s="170"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="212" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="249"/>
-      <c r="O6" s="249"/>
-      <c r="P6" s="250"/>
-      <c r="Q6" s="250"/>
-      <c r="R6" s="250"/>
-      <c r="S6" s="250"/>
-      <c r="T6" s="250"/>
-      <c r="U6" s="250"/>
-      <c r="V6" s="250"/>
-      <c r="W6" s="251"/>
+      <c r="N6" s="213"/>
+      <c r="O6" s="213"/>
+      <c r="P6" s="214"/>
+      <c r="Q6" s="214"/>
+      <c r="R6" s="214"/>
+      <c r="S6" s="214"/>
+      <c r="T6" s="214"/>
+      <c r="U6" s="214"/>
+      <c r="V6" s="214"/>
+      <c r="W6" s="215"/>
     </row>
     <row r="7" spans="2:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="274"/>
-      <c r="E7" s="275"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="76"/>
-      <c r="M7" s="179" t="s">
+      <c r="D7" s="171"/>
+      <c r="E7" s="172"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="216" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="180"/>
-      <c r="O7" s="180"/>
-      <c r="P7" s="244"/>
-      <c r="Q7" s="244"/>
-      <c r="R7" s="244"/>
-      <c r="S7" s="244"/>
-      <c r="T7" s="244"/>
-      <c r="U7" s="244"/>
-      <c r="V7" s="244"/>
-      <c r="W7" s="245"/>
+      <c r="N7" s="217"/>
+      <c r="O7" s="217"/>
+      <c r="P7" s="208"/>
+      <c r="Q7" s="208"/>
+      <c r="R7" s="208"/>
+      <c r="S7" s="208"/>
+      <c r="T7" s="208"/>
+      <c r="U7" s="208"/>
+      <c r="V7" s="208"/>
+      <c r="W7" s="209"/>
     </row>
     <row r="8" spans="2:24" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="274"/>
-      <c r="E8" s="275"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="75"/>
-      <c r="L8" s="76"/>
-      <c r="M8" s="252" t="s">
+      <c r="D8" s="171"/>
+      <c r="E8" s="172"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="N8" s="253"/>
-      <c r="O8" s="253"/>
-      <c r="P8" s="246"/>
-      <c r="Q8" s="246"/>
-      <c r="R8" s="246"/>
-      <c r="S8" s="246"/>
-      <c r="T8" s="246"/>
-      <c r="U8" s="246"/>
-      <c r="V8" s="246"/>
-      <c r="W8" s="247"/>
+      <c r="N8" s="219"/>
+      <c r="O8" s="219"/>
+      <c r="P8" s="210"/>
+      <c r="Q8" s="210"/>
+      <c r="R8" s="210"/>
+      <c r="S8" s="210"/>
+      <c r="T8" s="210"/>
+      <c r="U8" s="210"/>
+      <c r="V8" s="210"/>
+      <c r="W8" s="211"/>
     </row>
     <row r="9" spans="2:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="274"/>
-      <c r="E9" s="275"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="101"/>
-      <c r="K9" s="101"/>
-      <c r="L9" s="77"/>
-      <c r="M9" s="258" t="s">
+      <c r="D9" s="171"/>
+      <c r="E9" s="172"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="224" t="s">
         <v>4</v>
       </c>
-      <c r="N9" s="259"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="256" t="s">
+      <c r="N9" s="225"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="222" t="s">
         <v>27</v>
       </c>
-      <c r="Q9" s="256" t="s">
+      <c r="Q9" s="222" t="s">
         <v>28</v>
       </c>
-      <c r="R9" s="256" t="s">
+      <c r="R9" s="222" t="s">
         <v>29</v>
       </c>
-      <c r="S9" s="254" t="s">
+      <c r="S9" s="220" t="s">
         <v>30</v>
       </c>
-      <c r="T9" s="254"/>
-      <c r="U9" s="256" t="s">
+      <c r="T9" s="220"/>
+      <c r="U9" s="222" t="s">
         <v>34</v>
       </c>
-      <c r="V9" s="256" t="s">
+      <c r="V9" s="222" t="s">
         <v>31</v>
       </c>
-      <c r="W9" s="260"/>
+      <c r="W9" s="226"/>
     </row>
     <row r="10" spans="2:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="274"/>
-      <c r="E10" s="275"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="78"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="78"/>
-      <c r="M10" s="261" t="s">
+      <c r="D10" s="171"/>
+      <c r="E10" s="172"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="227" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="262"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="257"/>
-      <c r="Q10" s="257"/>
-      <c r="R10" s="257"/>
-      <c r="S10" s="255"/>
-      <c r="T10" s="255"/>
-      <c r="U10" s="257"/>
-      <c r="V10" s="70" t="s">
+      <c r="N10" s="228"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="223"/>
+      <c r="Q10" s="223"/>
+      <c r="R10" s="223"/>
+      <c r="S10" s="221"/>
+      <c r="T10" s="221"/>
+      <c r="U10" s="223"/>
+      <c r="V10" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="W10" s="38" t="s">
+      <c r="W10" s="36" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="274"/>
-      <c r="E11" s="275"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="81"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="264" t="s">
+      <c r="D11" s="171"/>
+      <c r="E11" s="172"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="76"/>
+      <c r="L11" s="76"/>
+      <c r="M11" s="158" t="s">
         <v>38</v>
       </c>
-      <c r="N11" s="265"/>
-      <c r="O11" s="266"/>
+      <c r="N11" s="159"/>
+      <c r="O11" s="160"/>
       <c r="P11" s="20"/>
       <c r="Q11" s="21"/>
       <c r="R11" s="22"/>
-      <c r="S11" s="127"/>
+      <c r="S11" s="122"/>
       <c r="T11" s="28"/>
-      <c r="U11" s="71"/>
+      <c r="U11" s="68"/>
       <c r="V11" s="30"/>
-      <c r="W11" s="39"/>
+      <c r="W11" s="37"/>
     </row>
     <row r="12" spans="2:24" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="276"/>
-      <c r="E12" s="277"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="109"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="111"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="264" t="s">
+      <c r="D12" s="173"/>
+      <c r="E12" s="174"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="106"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="158" t="s">
         <v>2</v>
       </c>
-      <c r="N12" s="265"/>
-      <c r="O12" s="266"/>
+      <c r="N12" s="159"/>
+      <c r="O12" s="160"/>
       <c r="P12" s="20"/>
       <c r="Q12" s="21"/>
       <c r="R12" s="23"/>
-      <c r="S12" s="127"/>
+      <c r="S12" s="122"/>
       <c r="T12" s="28"/>
-      <c r="U12" s="71"/>
+      <c r="U12" s="68"/>
       <c r="V12" s="30"/>
-      <c r="W12" s="39"/>
+      <c r="W12" s="37"/>
     </row>
     <row r="13" spans="2:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="66"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="63"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="84"/>
-      <c r="M13" s="264" t="s">
+      <c r="J13" s="78"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="N13" s="265"/>
-      <c r="O13" s="266"/>
-      <c r="P13" s="72"/>
+      <c r="N13" s="159"/>
+      <c r="O13" s="160"/>
+      <c r="P13" s="69"/>
       <c r="Q13" s="23"/>
       <c r="R13" s="23"/>
-      <c r="S13" s="127"/>
+      <c r="S13" s="122"/>
       <c r="T13" s="28"/>
-      <c r="U13" s="71"/>
+      <c r="U13" s="68"/>
       <c r="V13" s="30"/>
-      <c r="W13" s="39"/>
+      <c r="W13" s="37"/>
     </row>
     <row r="14" spans="2:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="64"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="61"/>
       <c r="H14" s="3"/>
       <c r="I14" s="8"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="81"/>
-      <c r="M14" s="192" t="s">
+      <c r="J14" s="76"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="76"/>
+      <c r="M14" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="N14" s="193"/>
-      <c r="O14" s="194"/>
-      <c r="P14" s="271"/>
-      <c r="Q14" s="291"/>
-      <c r="R14" s="291"/>
-      <c r="S14" s="294"/>
-      <c r="T14" s="297"/>
-      <c r="U14" s="270"/>
-      <c r="V14" s="185"/>
-      <c r="W14" s="188"/>
+      <c r="N14" s="166"/>
+      <c r="O14" s="167"/>
+      <c r="P14" s="168"/>
+      <c r="Q14" s="187"/>
+      <c r="R14" s="187"/>
+      <c r="S14" s="190"/>
+      <c r="T14" s="193"/>
+      <c r="U14" s="164"/>
+      <c r="V14" s="286"/>
+      <c r="W14" s="289"/>
     </row>
     <row r="15" spans="2:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="61"/>
       <c r="H15" s="3"/>
       <c r="I15" s="8"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="192"/>
-      <c r="N15" s="193"/>
-      <c r="O15" s="194"/>
-      <c r="P15" s="271"/>
-      <c r="Q15" s="292"/>
-      <c r="R15" s="292"/>
-      <c r="S15" s="295"/>
-      <c r="T15" s="298"/>
-      <c r="U15" s="270"/>
-      <c r="V15" s="186"/>
-      <c r="W15" s="189"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="76"/>
+      <c r="M15" s="165"/>
+      <c r="N15" s="166"/>
+      <c r="O15" s="167"/>
+      <c r="P15" s="168"/>
+      <c r="Q15" s="188"/>
+      <c r="R15" s="188"/>
+      <c r="S15" s="191"/>
+      <c r="T15" s="194"/>
+      <c r="U15" s="164"/>
+      <c r="V15" s="287"/>
+      <c r="W15" s="290"/>
     </row>
     <row r="16" spans="2:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="64"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="61"/>
       <c r="H16" s="3"/>
       <c r="I16" s="8"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="192"/>
-      <c r="N16" s="193"/>
-      <c r="O16" s="194"/>
-      <c r="P16" s="271"/>
-      <c r="Q16" s="292"/>
-      <c r="R16" s="292"/>
-      <c r="S16" s="295"/>
-      <c r="T16" s="298"/>
-      <c r="U16" s="270"/>
-      <c r="V16" s="186"/>
-      <c r="W16" s="190"/>
-      <c r="X16" s="133"/>
+      <c r="J16" s="76"/>
+      <c r="K16" s="76"/>
+      <c r="L16" s="76"/>
+      <c r="M16" s="165"/>
+      <c r="N16" s="166"/>
+      <c r="O16" s="167"/>
+      <c r="P16" s="168"/>
+      <c r="Q16" s="188"/>
+      <c r="R16" s="188"/>
+      <c r="S16" s="191"/>
+      <c r="T16" s="194"/>
+      <c r="U16" s="164"/>
+      <c r="V16" s="287"/>
+      <c r="W16" s="291"/>
+      <c r="X16" s="128"/>
     </row>
     <row r="17" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="64"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="61"/>
       <c r="H17" s="3"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="192"/>
-      <c r="N17" s="193"/>
-      <c r="O17" s="194"/>
-      <c r="P17" s="271"/>
-      <c r="Q17" s="293"/>
-      <c r="R17" s="293"/>
-      <c r="S17" s="296"/>
-      <c r="T17" s="299"/>
-      <c r="U17" s="270"/>
-      <c r="V17" s="187"/>
-      <c r="W17" s="191"/>
+      <c r="J17" s="76"/>
+      <c r="K17" s="76"/>
+      <c r="L17" s="76"/>
+      <c r="M17" s="165"/>
+      <c r="N17" s="166"/>
+      <c r="O17" s="167"/>
+      <c r="P17" s="168"/>
+      <c r="Q17" s="189"/>
+      <c r="R17" s="189"/>
+      <c r="S17" s="192"/>
+      <c r="T17" s="195"/>
+      <c r="U17" s="164"/>
+      <c r="V17" s="288"/>
+      <c r="W17" s="292"/>
     </row>
     <row r="18" spans="2:23" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="64"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="61"/>
       <c r="H18" s="3"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="267" t="s">
+      <c r="J18" s="76"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="76"/>
+      <c r="M18" s="161" t="s">
         <v>56</v>
       </c>
-      <c r="N18" s="268"/>
-      <c r="O18" s="269"/>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="41"/>
-      <c r="S18" s="137"/>
-      <c r="T18" s="138"/>
-      <c r="U18" s="42"/>
-      <c r="V18" s="43"/>
-      <c r="W18" s="44">
+      <c r="N18" s="162"/>
+      <c r="O18" s="163"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="39"/>
+      <c r="S18" s="132"/>
+      <c r="T18" s="133"/>
+      <c r="U18" s="40"/>
+      <c r="V18" s="41"/>
+      <c r="W18" s="42">
         <f>V18*(T18-S18)/1000</f>
         <v>0</v>
       </c>
@@ -4744,186 +4744,186 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="64"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="61"/>
       <c r="H19" s="3"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="303" t="s">
+      <c r="J19" s="76"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="76"/>
+      <c r="M19" s="199" t="s">
         <v>36</v>
       </c>
-      <c r="N19" s="304"/>
-      <c r="O19" s="305"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="309"/>
-      <c r="T19" s="310"/>
-      <c r="U19" s="36"/>
-      <c r="V19" s="73"/>
-      <c r="W19" s="74"/>
+      <c r="N19" s="200"/>
+      <c r="O19" s="201"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="138"/>
+      <c r="T19" s="139"/>
+      <c r="U19" s="34"/>
+      <c r="V19" s="320"/>
+      <c r="W19" s="321"/>
     </row>
     <row r="20" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="113"/>
-      <c r="I20" s="114"/>
-      <c r="J20" s="115"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="115"/>
-      <c r="M20" s="192"/>
-      <c r="N20" s="193"/>
-      <c r="O20" s="193"/>
-      <c r="P20" s="193"/>
-      <c r="Q20" s="194"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="108"/>
+      <c r="I20" s="109"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="165"/>
+      <c r="N20" s="166"/>
+      <c r="O20" s="166"/>
+      <c r="P20" s="166"/>
+      <c r="Q20" s="167"/>
       <c r="R20" s="24"/>
-      <c r="S20" s="134"/>
-      <c r="T20" s="135"/>
-      <c r="U20" s="136"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="39"/>
+      <c r="S20" s="129"/>
+      <c r="T20" s="130"/>
+      <c r="U20" s="131"/>
+      <c r="V20" s="318"/>
+      <c r="W20" s="319"/>
     </row>
     <row r="21" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="129"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="117"/>
-      <c r="L21" s="117"/>
-      <c r="M21" s="300"/>
-      <c r="N21" s="301"/>
-      <c r="O21" s="302"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="124"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="112"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="196"/>
+      <c r="N21" s="197"/>
+      <c r="O21" s="198"/>
       <c r="P21" s="25"/>
       <c r="Q21" s="26"/>
       <c r="R21" s="27"/>
-      <c r="S21" s="128"/>
+      <c r="S21" s="123"/>
       <c r="T21" s="29"/>
-      <c r="U21" s="32"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="45"/>
+      <c r="U21" s="317"/>
+      <c r="V21" s="318"/>
+      <c r="W21" s="319"/>
     </row>
     <row r="22" spans="2:23" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="129"/>
-      <c r="I22" s="131"/>
-      <c r="J22" s="126"/>
-      <c r="K22" s="118"/>
-      <c r="L22" s="118"/>
-      <c r="M22" s="306" t="s">
+      <c r="F22" s="60"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="124"/>
+      <c r="I22" s="126"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="113"/>
+      <c r="L22" s="113"/>
+      <c r="M22" s="202" t="s">
         <v>40</v>
       </c>
-      <c r="N22" s="307"/>
-      <c r="O22" s="308"/>
-      <c r="P22" s="102"/>
-      <c r="Q22" s="103"/>
-      <c r="R22" s="102"/>
-      <c r="S22" s="158"/>
-      <c r="T22" s="159"/>
-      <c r="U22" s="104"/>
-      <c r="V22" s="105"/>
-      <c r="W22" s="106"/>
+      <c r="N22" s="203"/>
+      <c r="O22" s="204"/>
+      <c r="P22" s="97"/>
+      <c r="Q22" s="98"/>
+      <c r="R22" s="97"/>
+      <c r="S22" s="293"/>
+      <c r="T22" s="294"/>
+      <c r="U22" s="99"/>
+      <c r="V22" s="100"/>
+      <c r="W22" s="101"/>
     </row>
     <row r="23" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="132"/>
-      <c r="I23" s="130"/>
-      <c r="J23" s="119"/>
-      <c r="K23" s="120"/>
-      <c r="L23" s="121"/>
-      <c r="M23" s="285" t="s">
+      <c r="F23" s="54"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="115"/>
+      <c r="L23" s="116"/>
+      <c r="M23" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="N23" s="285"/>
-      <c r="O23" s="285"/>
-      <c r="P23" s="285"/>
-      <c r="Q23" s="285"/>
-      <c r="R23" s="285"/>
-      <c r="S23" s="285"/>
-      <c r="T23" s="285"/>
-      <c r="U23" s="285"/>
-      <c r="V23" s="285"/>
-      <c r="W23" s="285"/>
+      <c r="N23" s="144"/>
+      <c r="O23" s="144"/>
+      <c r="P23" s="144"/>
+      <c r="Q23" s="144"/>
+      <c r="R23" s="144"/>
+      <c r="S23" s="144"/>
+      <c r="T23" s="144"/>
+      <c r="U23" s="144"/>
+      <c r="V23" s="144"/>
+      <c r="W23" s="144"/>
     </row>
     <row r="24" spans="2:23" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="112"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="123"/>
-      <c r="K24" s="115" t="s">
+      <c r="F24" s="54"/>
+      <c r="G24" s="107"/>
+      <c r="H24" s="117"/>
+      <c r="I24" s="117"/>
+      <c r="J24" s="118"/>
+      <c r="K24" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="L24" s="115"/>
-      <c r="M24" s="285"/>
-      <c r="N24" s="285"/>
-      <c r="O24" s="285"/>
-      <c r="P24" s="285"/>
-      <c r="Q24" s="285"/>
-      <c r="R24" s="285"/>
-      <c r="S24" s="285"/>
-      <c r="T24" s="285"/>
-      <c r="U24" s="285"/>
-      <c r="V24" s="285"/>
-      <c r="W24" s="285"/>
+      <c r="L24" s="110"/>
+      <c r="M24" s="144"/>
+      <c r="N24" s="144"/>
+      <c r="O24" s="144"/>
+      <c r="P24" s="144"/>
+      <c r="Q24" s="144"/>
+      <c r="R24" s="144"/>
+      <c r="S24" s="144"/>
+      <c r="T24" s="144"/>
+      <c r="U24" s="144"/>
+      <c r="V24" s="144"/>
+      <c r="W24" s="144"/>
     </row>
     <row r="25" spans="2:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="115"/>
-      <c r="I25" s="115"/>
-      <c r="J25" s="125"/>
-      <c r="K25" s="116"/>
-      <c r="L25" s="117"/>
-      <c r="M25" s="287" t="s">
+      <c r="F25" s="54"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="120"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="183" t="s">
         <v>46</v>
       </c>
-      <c r="N25" s="288"/>
-      <c r="O25" s="284" t="s">
+      <c r="N25" s="184"/>
+      <c r="O25" s="153" t="s">
         <v>43</v>
       </c>
-      <c r="P25" s="284"/>
-      <c r="Q25" s="284" t="s">
+      <c r="P25" s="153"/>
+      <c r="Q25" s="153" t="s">
         <v>35</v>
       </c>
-      <c r="R25" s="284"/>
-      <c r="S25" s="284"/>
-      <c r="T25" s="284"/>
-      <c r="U25" s="284" t="s">
+      <c r="R25" s="153"/>
+      <c r="S25" s="153"/>
+      <c r="T25" s="153"/>
+      <c r="U25" s="153" t="s">
         <v>59</v>
       </c>
-      <c r="V25" s="161" t="s">
+      <c r="V25" s="298" t="s">
         <v>61</v>
       </c>
-      <c r="W25" s="163" t="s">
+      <c r="W25" s="299" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4932,414 +4932,414 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="124"/>
-      <c r="I26" s="124"/>
-      <c r="J26" s="282"/>
-      <c r="K26" s="282"/>
-      <c r="L26" s="283"/>
-      <c r="M26" s="289"/>
-      <c r="N26" s="290"/>
-      <c r="O26" s="162"/>
-      <c r="P26" s="162"/>
-      <c r="Q26" s="281" t="s">
+      <c r="F26" s="54"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="180"/>
+      <c r="K26" s="180"/>
+      <c r="L26" s="181"/>
+      <c r="M26" s="185"/>
+      <c r="N26" s="186"/>
+      <c r="O26" s="154"/>
+      <c r="P26" s="154"/>
+      <c r="Q26" s="157" t="s">
         <v>15</v>
       </c>
-      <c r="R26" s="281"/>
-      <c r="S26" s="281" t="s">
+      <c r="R26" s="157"/>
+      <c r="S26" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="T26" s="281"/>
-      <c r="U26" s="162"/>
-      <c r="V26" s="162"/>
-      <c r="W26" s="164"/>
+      <c r="T26" s="157"/>
+      <c r="U26" s="154"/>
+      <c r="V26" s="154"/>
+      <c r="W26" s="300"/>
     </row>
     <row r="27" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="124"/>
-      <c r="I27" s="124"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="115"/>
-      <c r="M27" s="170"/>
-      <c r="N27" s="171"/>
-      <c r="O27" s="172"/>
-      <c r="P27" s="172"/>
-      <c r="Q27" s="173"/>
-      <c r="R27" s="173"/>
-      <c r="S27" s="173"/>
-      <c r="T27" s="173"/>
-      <c r="U27" s="50"/>
-      <c r="V27" s="55"/>
-      <c r="W27" s="139"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="119"/>
+      <c r="I27" s="119"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="110"/>
+      <c r="L27" s="110"/>
+      <c r="M27" s="147"/>
+      <c r="N27" s="148"/>
+      <c r="O27" s="145"/>
+      <c r="P27" s="145"/>
+      <c r="Q27" s="146"/>
+      <c r="R27" s="146"/>
+      <c r="S27" s="146"/>
+      <c r="T27" s="146"/>
+      <c r="U27" s="47"/>
+      <c r="V27" s="52"/>
+      <c r="W27" s="134"/>
     </row>
     <row r="28" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="58"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="55"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="81"/>
-      <c r="L28" s="81"/>
-      <c r="M28" s="170"/>
-      <c r="N28" s="171"/>
-      <c r="O28" s="172"/>
-      <c r="P28" s="172"/>
-      <c r="Q28" s="173"/>
-      <c r="R28" s="173"/>
-      <c r="S28" s="173"/>
-      <c r="T28" s="173"/>
-      <c r="U28" s="50"/>
-      <c r="V28" s="55"/>
-      <c r="W28" s="139"/>
+      <c r="J28" s="76"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="76"/>
+      <c r="M28" s="147"/>
+      <c r="N28" s="148"/>
+      <c r="O28" s="145"/>
+      <c r="P28" s="145"/>
+      <c r="Q28" s="146"/>
+      <c r="R28" s="146"/>
+      <c r="S28" s="146"/>
+      <c r="T28" s="146"/>
+      <c r="U28" s="47"/>
+      <c r="V28" s="52"/>
+      <c r="W28" s="134"/>
     </row>
     <row r="29" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="58"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="55"/>
       <c r="H29" s="3"/>
       <c r="I29" s="17"/>
-      <c r="J29" s="278"/>
-      <c r="K29" s="278"/>
-      <c r="L29" s="278"/>
-      <c r="M29" s="170"/>
-      <c r="N29" s="171"/>
-      <c r="O29" s="172"/>
-      <c r="P29" s="172"/>
-      <c r="Q29" s="173"/>
-      <c r="R29" s="173"/>
-      <c r="S29" s="173"/>
-      <c r="T29" s="173"/>
-      <c r="U29" s="50"/>
-      <c r="V29" s="55"/>
-      <c r="W29" s="139"/>
+      <c r="J29" s="175"/>
+      <c r="K29" s="175"/>
+      <c r="L29" s="175"/>
+      <c r="M29" s="147"/>
+      <c r="N29" s="148"/>
+      <c r="O29" s="145"/>
+      <c r="P29" s="145"/>
+      <c r="Q29" s="146"/>
+      <c r="R29" s="146"/>
+      <c r="S29" s="146"/>
+      <c r="T29" s="146"/>
+      <c r="U29" s="47"/>
+      <c r="V29" s="52"/>
+      <c r="W29" s="134"/>
     </row>
     <row r="30" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="58"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="55"/>
       <c r="H30" s="3"/>
       <c r="I30" s="17"/>
-      <c r="J30" s="165"/>
-      <c r="K30" s="165"/>
-      <c r="L30" s="166"/>
-      <c r="M30" s="170"/>
-      <c r="N30" s="171"/>
-      <c r="O30" s="172"/>
-      <c r="P30" s="172"/>
-      <c r="Q30" s="173"/>
-      <c r="R30" s="173"/>
-      <c r="S30" s="173"/>
-      <c r="T30" s="173"/>
-      <c r="U30" s="50"/>
-      <c r="V30" s="55"/>
-      <c r="W30" s="139"/>
+      <c r="J30" s="178"/>
+      <c r="K30" s="178"/>
+      <c r="L30" s="179"/>
+      <c r="M30" s="147"/>
+      <c r="N30" s="148"/>
+      <c r="O30" s="145"/>
+      <c r="P30" s="145"/>
+      <c r="Q30" s="146"/>
+      <c r="R30" s="146"/>
+      <c r="S30" s="146"/>
+      <c r="T30" s="146"/>
+      <c r="U30" s="47"/>
+      <c r="V30" s="52"/>
+      <c r="W30" s="134"/>
     </row>
     <row r="31" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="58"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="55"/>
       <c r="H31" s="3"/>
       <c r="I31" s="17"/>
-      <c r="J31" s="165"/>
-      <c r="K31" s="165"/>
-      <c r="L31" s="166"/>
-      <c r="M31" s="170"/>
-      <c r="N31" s="171"/>
-      <c r="O31" s="172"/>
-      <c r="P31" s="172"/>
-      <c r="Q31" s="173"/>
-      <c r="R31" s="173"/>
-      <c r="S31" s="173"/>
-      <c r="T31" s="173"/>
-      <c r="U31" s="50"/>
-      <c r="V31" s="55"/>
-      <c r="W31" s="139"/>
+      <c r="J31" s="178"/>
+      <c r="K31" s="178"/>
+      <c r="L31" s="179"/>
+      <c r="M31" s="147"/>
+      <c r="N31" s="148"/>
+      <c r="O31" s="145"/>
+      <c r="P31" s="145"/>
+      <c r="Q31" s="146"/>
+      <c r="R31" s="146"/>
+      <c r="S31" s="146"/>
+      <c r="T31" s="146"/>
+      <c r="U31" s="47"/>
+      <c r="V31" s="52"/>
+      <c r="W31" s="134"/>
     </row>
     <row r="32" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="165"/>
-      <c r="K32" s="165"/>
-      <c r="L32" s="166"/>
-      <c r="M32" s="170"/>
-      <c r="N32" s="171"/>
-      <c r="O32" s="172"/>
-      <c r="P32" s="172"/>
-      <c r="Q32" s="173"/>
-      <c r="R32" s="173"/>
-      <c r="S32" s="173"/>
-      <c r="T32" s="173"/>
-      <c r="U32" s="50"/>
-      <c r="V32" s="55"/>
-      <c r="W32" s="139"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="81"/>
+      <c r="J32" s="178"/>
+      <c r="K32" s="178"/>
+      <c r="L32" s="179"/>
+      <c r="M32" s="147"/>
+      <c r="N32" s="148"/>
+      <c r="O32" s="145"/>
+      <c r="P32" s="145"/>
+      <c r="Q32" s="146"/>
+      <c r="R32" s="146"/>
+      <c r="S32" s="146"/>
+      <c r="T32" s="146"/>
+      <c r="U32" s="47"/>
+      <c r="V32" s="52"/>
+      <c r="W32" s="134"/>
     </row>
     <row r="33" spans="2:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="86"/>
-      <c r="J33" s="165"/>
-      <c r="K33" s="165"/>
-      <c r="L33" s="166"/>
-      <c r="M33" s="170"/>
-      <c r="N33" s="171"/>
-      <c r="O33" s="172"/>
-      <c r="P33" s="172"/>
-      <c r="Q33" s="173"/>
-      <c r="R33" s="173"/>
-      <c r="S33" s="173"/>
-      <c r="T33" s="173"/>
-      <c r="U33" s="50"/>
-      <c r="V33" s="55"/>
-      <c r="W33" s="139"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="178"/>
+      <c r="K33" s="178"/>
+      <c r="L33" s="179"/>
+      <c r="M33" s="147"/>
+      <c r="N33" s="148"/>
+      <c r="O33" s="145"/>
+      <c r="P33" s="145"/>
+      <c r="Q33" s="146"/>
+      <c r="R33" s="146"/>
+      <c r="S33" s="146"/>
+      <c r="T33" s="146"/>
+      <c r="U33" s="47"/>
+      <c r="V33" s="52"/>
+      <c r="W33" s="134"/>
     </row>
     <row r="34" spans="2:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="86"/>
-      <c r="J34" s="165"/>
-      <c r="K34" s="165"/>
-      <c r="L34" s="166"/>
-      <c r="M34" s="170"/>
-      <c r="N34" s="171"/>
-      <c r="O34" s="172"/>
-      <c r="P34" s="172"/>
-      <c r="Q34" s="173"/>
-      <c r="R34" s="173"/>
-      <c r="S34" s="173"/>
-      <c r="T34" s="173"/>
-      <c r="U34" s="50"/>
-      <c r="V34" s="55"/>
-      <c r="W34" s="139"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="178"/>
+      <c r="K34" s="178"/>
+      <c r="L34" s="179"/>
+      <c r="M34" s="147"/>
+      <c r="N34" s="148"/>
+      <c r="O34" s="145"/>
+      <c r="P34" s="145"/>
+      <c r="Q34" s="146"/>
+      <c r="R34" s="146"/>
+      <c r="S34" s="146"/>
+      <c r="T34" s="146"/>
+      <c r="U34" s="47"/>
+      <c r="V34" s="52"/>
+      <c r="W34" s="134"/>
     </row>
     <row r="35" spans="2:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="86"/>
-      <c r="J35" s="165"/>
-      <c r="K35" s="165"/>
-      <c r="L35" s="166"/>
-      <c r="M35" s="170"/>
-      <c r="N35" s="171"/>
-      <c r="O35" s="172"/>
-      <c r="P35" s="172"/>
-      <c r="Q35" s="173"/>
-      <c r="R35" s="173"/>
-      <c r="S35" s="173"/>
-      <c r="T35" s="173"/>
-      <c r="U35" s="50"/>
-      <c r="V35" s="55"/>
-      <c r="W35" s="139"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="81"/>
+      <c r="J35" s="178"/>
+      <c r="K35" s="178"/>
+      <c r="L35" s="179"/>
+      <c r="M35" s="147"/>
+      <c r="N35" s="148"/>
+      <c r="O35" s="145"/>
+      <c r="P35" s="145"/>
+      <c r="Q35" s="146"/>
+      <c r="R35" s="146"/>
+      <c r="S35" s="146"/>
+      <c r="T35" s="146"/>
+      <c r="U35" s="47"/>
+      <c r="V35" s="52"/>
+      <c r="W35" s="134"/>
     </row>
     <row r="36" spans="2:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="86"/>
-      <c r="J36" s="165"/>
-      <c r="K36" s="165"/>
-      <c r="L36" s="166"/>
-      <c r="M36" s="170"/>
-      <c r="N36" s="171"/>
-      <c r="O36" s="172"/>
-      <c r="P36" s="172"/>
-      <c r="Q36" s="173"/>
-      <c r="R36" s="173"/>
-      <c r="S36" s="173"/>
-      <c r="T36" s="173"/>
-      <c r="U36" s="50"/>
-      <c r="V36" s="55"/>
-      <c r="W36" s="139"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="178"/>
+      <c r="K36" s="178"/>
+      <c r="L36" s="179"/>
+      <c r="M36" s="147"/>
+      <c r="N36" s="148"/>
+      <c r="O36" s="145"/>
+      <c r="P36" s="145"/>
+      <c r="Q36" s="146"/>
+      <c r="R36" s="146"/>
+      <c r="S36" s="146"/>
+      <c r="T36" s="146"/>
+      <c r="U36" s="47"/>
+      <c r="V36" s="52"/>
+      <c r="W36" s="134"/>
     </row>
     <row r="37" spans="2:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="86"/>
-      <c r="J37" s="165"/>
-      <c r="K37" s="165"/>
-      <c r="L37" s="166"/>
-      <c r="M37" s="170"/>
-      <c r="N37" s="171"/>
-      <c r="O37" s="172"/>
-      <c r="P37" s="172"/>
-      <c r="Q37" s="173"/>
-      <c r="R37" s="173"/>
-      <c r="S37" s="173"/>
-      <c r="T37" s="173"/>
-      <c r="U37" s="50"/>
-      <c r="V37" s="55"/>
-      <c r="W37" s="139"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="81"/>
+      <c r="J37" s="178"/>
+      <c r="K37" s="178"/>
+      <c r="L37" s="179"/>
+      <c r="M37" s="147"/>
+      <c r="N37" s="148"/>
+      <c r="O37" s="145"/>
+      <c r="P37" s="145"/>
+      <c r="Q37" s="146"/>
+      <c r="R37" s="146"/>
+      <c r="S37" s="146"/>
+      <c r="T37" s="146"/>
+      <c r="U37" s="47"/>
+      <c r="V37" s="52"/>
+      <c r="W37" s="134"/>
     </row>
     <row r="38" spans="2:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="86"/>
-      <c r="J38" s="165"/>
-      <c r="K38" s="165"/>
-      <c r="L38" s="166"/>
-      <c r="M38" s="170"/>
-      <c r="N38" s="171"/>
-      <c r="O38" s="172"/>
-      <c r="P38" s="172"/>
-      <c r="Q38" s="173"/>
-      <c r="R38" s="173"/>
-      <c r="S38" s="173"/>
-      <c r="T38" s="173"/>
-      <c r="U38" s="50"/>
-      <c r="V38" s="55"/>
-      <c r="W38" s="139"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="178"/>
+      <c r="K38" s="178"/>
+      <c r="L38" s="179"/>
+      <c r="M38" s="147"/>
+      <c r="N38" s="148"/>
+      <c r="O38" s="145"/>
+      <c r="P38" s="145"/>
+      <c r="Q38" s="146"/>
+      <c r="R38" s="146"/>
+      <c r="S38" s="146"/>
+      <c r="T38" s="146"/>
+      <c r="U38" s="47"/>
+      <c r="V38" s="52"/>
+      <c r="W38" s="134"/>
     </row>
     <row r="39" spans="2:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="86"/>
-      <c r="J39" s="165"/>
-      <c r="K39" s="165"/>
-      <c r="L39" s="166"/>
-      <c r="M39" s="170"/>
-      <c r="N39" s="171"/>
-      <c r="O39" s="172"/>
-      <c r="P39" s="172"/>
-      <c r="Q39" s="173"/>
-      <c r="R39" s="173"/>
-      <c r="S39" s="173"/>
-      <c r="T39" s="173"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="55"/>
-      <c r="W39" s="139"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="81"/>
+      <c r="J39" s="178"/>
+      <c r="K39" s="178"/>
+      <c r="L39" s="179"/>
+      <c r="M39" s="147"/>
+      <c r="N39" s="148"/>
+      <c r="O39" s="145"/>
+      <c r="P39" s="145"/>
+      <c r="Q39" s="146"/>
+      <c r="R39" s="146"/>
+      <c r="S39" s="146"/>
+      <c r="T39" s="146"/>
+      <c r="U39" s="47"/>
+      <c r="V39" s="52"/>
+      <c r="W39" s="134"/>
     </row>
     <row r="40" spans="2:25" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="165"/>
-      <c r="K40" s="165"/>
-      <c r="L40" s="166"/>
-      <c r="M40" s="167"/>
-      <c r="N40" s="168"/>
-      <c r="O40" s="239"/>
-      <c r="P40" s="239"/>
-      <c r="Q40" s="240"/>
-      <c r="R40" s="240"/>
-      <c r="S40" s="240"/>
-      <c r="T40" s="240"/>
-      <c r="U40" s="51"/>
-      <c r="V40" s="56"/>
-      <c r="W40" s="140"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="81"/>
+      <c r="J40" s="178"/>
+      <c r="K40" s="178"/>
+      <c r="L40" s="179"/>
+      <c r="M40" s="234"/>
+      <c r="N40" s="235"/>
+      <c r="O40" s="236"/>
+      <c r="P40" s="236"/>
+      <c r="Q40" s="237"/>
+      <c r="R40" s="237"/>
+      <c r="S40" s="237"/>
+      <c r="T40" s="237"/>
+      <c r="U40" s="48"/>
+      <c r="V40" s="53"/>
+      <c r="W40" s="135"/>
     </row>
     <row r="41" spans="2:25" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="86"/>
-      <c r="J41" s="165"/>
-      <c r="K41" s="165"/>
-      <c r="L41" s="166"/>
-      <c r="M41" s="167"/>
-      <c r="N41" s="168"/>
-      <c r="O41" s="168"/>
-      <c r="P41" s="168"/>
-      <c r="Q41" s="169"/>
-      <c r="R41" s="169"/>
-      <c r="S41" s="169"/>
-      <c r="T41" s="169"/>
-      <c r="U41" s="51"/>
-      <c r="V41" s="56"/>
-      <c r="W41" s="140"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="81"/>
+      <c r="J41" s="178"/>
+      <c r="K41" s="178"/>
+      <c r="L41" s="179"/>
+      <c r="M41" s="234"/>
+      <c r="N41" s="235"/>
+      <c r="O41" s="235"/>
+      <c r="P41" s="235"/>
+      <c r="Q41" s="301"/>
+      <c r="R41" s="301"/>
+      <c r="S41" s="301"/>
+      <c r="T41" s="301"/>
+      <c r="U41" s="48"/>
+      <c r="V41" s="53"/>
+      <c r="W41" s="135"/>
     </row>
     <row r="42" spans="2:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="81"/>
-      <c r="I42" s="81"/>
-      <c r="J42" s="81"/>
-      <c r="K42" s="81"/>
-      <c r="L42" s="81"/>
-      <c r="M42" s="285" t="s">
+      <c r="F42" s="54"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="76"/>
+      <c r="I42" s="76"/>
+      <c r="J42" s="76"/>
+      <c r="K42" s="76"/>
+      <c r="L42" s="76"/>
+      <c r="M42" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="N42" s="285"/>
-      <c r="O42" s="285"/>
-      <c r="P42" s="285"/>
-      <c r="Q42" s="285"/>
-      <c r="R42" s="285"/>
-      <c r="S42" s="285"/>
-      <c r="T42" s="285"/>
-      <c r="U42" s="285"/>
-      <c r="V42" s="285"/>
-      <c r="W42" s="285"/>
+      <c r="N42" s="144"/>
+      <c r="O42" s="144"/>
+      <c r="P42" s="144"/>
+      <c r="Q42" s="144"/>
+      <c r="R42" s="144"/>
+      <c r="S42" s="144"/>
+      <c r="T42" s="144"/>
+      <c r="U42" s="144"/>
+      <c r="V42" s="144"/>
+      <c r="W42" s="144"/>
     </row>
     <row r="43" spans="2:25" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
@@ -5348,576 +5348,576 @@
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="85"/>
-      <c r="I43" s="85"/>
-      <c r="J43" s="85"/>
-      <c r="K43" s="87"/>
-      <c r="L43" s="76"/>
-      <c r="M43" s="286"/>
-      <c r="N43" s="286"/>
-      <c r="O43" s="286"/>
-      <c r="P43" s="286"/>
-      <c r="Q43" s="286"/>
-      <c r="R43" s="286"/>
-      <c r="S43" s="286"/>
-      <c r="T43" s="286"/>
-      <c r="U43" s="286"/>
-      <c r="V43" s="286"/>
-      <c r="W43" s="286"/>
-      <c r="Y43" s="141"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="80"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="82"/>
+      <c r="L43" s="71"/>
+      <c r="M43" s="182"/>
+      <c r="N43" s="182"/>
+      <c r="O43" s="182"/>
+      <c r="P43" s="182"/>
+      <c r="Q43" s="182"/>
+      <c r="R43" s="182"/>
+      <c r="S43" s="182"/>
+      <c r="T43" s="182"/>
+      <c r="U43" s="182"/>
+      <c r="V43" s="182"/>
+      <c r="W43" s="182"/>
+      <c r="Y43" s="136"/>
     </row>
     <row r="44" spans="2:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="85"/>
-      <c r="I44" s="85"/>
-      <c r="J44" s="85"/>
-      <c r="K44" s="87"/>
-      <c r="L44" s="76"/>
-      <c r="M44" s="313" t="s">
+      <c r="F44" s="54"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="80"/>
+      <c r="I44" s="80"/>
+      <c r="J44" s="80"/>
+      <c r="K44" s="82"/>
+      <c r="L44" s="71"/>
+      <c r="M44" s="155" t="s">
         <v>63</v>
       </c>
-      <c r="N44" s="314"/>
-      <c r="O44" s="314"/>
-      <c r="P44" s="314"/>
-      <c r="Q44" s="314"/>
-      <c r="R44" s="314"/>
-      <c r="S44" s="314"/>
-      <c r="T44" s="314"/>
-      <c r="U44" s="314"/>
-      <c r="V44" s="315"/>
-      <c r="W44" s="316"/>
+      <c r="N44" s="156"/>
+      <c r="O44" s="156"/>
+      <c r="P44" s="156"/>
+      <c r="Q44" s="156"/>
+      <c r="R44" s="156"/>
+      <c r="S44" s="156"/>
+      <c r="T44" s="156"/>
+      <c r="U44" s="156"/>
+      <c r="V44" s="149"/>
+      <c r="W44" s="150"/>
     </row>
     <row r="45" spans="2:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="85"/>
-      <c r="I45" s="85"/>
-      <c r="J45" s="85"/>
-      <c r="K45" s="87"/>
-      <c r="L45" s="76"/>
-      <c r="M45" s="221" t="s">
+      <c r="F45" s="54"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="80"/>
+      <c r="I45" s="80"/>
+      <c r="J45" s="80"/>
+      <c r="K45" s="82"/>
+      <c r="L45" s="71"/>
+      <c r="M45" s="242" t="s">
         <v>62</v>
       </c>
-      <c r="N45" s="222"/>
-      <c r="O45" s="222"/>
-      <c r="P45" s="222"/>
-      <c r="Q45" s="222"/>
-      <c r="R45" s="222"/>
-      <c r="S45" s="222"/>
-      <c r="T45" s="222"/>
-      <c r="U45" s="222"/>
-      <c r="V45" s="317"/>
-      <c r="W45" s="318"/>
+      <c r="N45" s="243"/>
+      <c r="O45" s="243"/>
+      <c r="P45" s="243"/>
+      <c r="Q45" s="243"/>
+      <c r="R45" s="243"/>
+      <c r="S45" s="243"/>
+      <c r="T45" s="243"/>
+      <c r="U45" s="243"/>
+      <c r="V45" s="151"/>
+      <c r="W45" s="152"/>
     </row>
     <row r="46" spans="2:25" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="85"/>
-      <c r="I46" s="85"/>
-      <c r="J46" s="85"/>
-      <c r="K46" s="76"/>
-      <c r="L46" s="76"/>
-      <c r="M46" s="279" t="s">
+      <c r="F46" s="54"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="80"/>
+      <c r="I46" s="80"/>
+      <c r="J46" s="80"/>
+      <c r="K46" s="71"/>
+      <c r="L46" s="71"/>
+      <c r="M46" s="176" t="s">
         <v>37</v>
       </c>
-      <c r="N46" s="280"/>
-      <c r="O46" s="280"/>
-      <c r="P46" s="280"/>
-      <c r="Q46" s="280"/>
-      <c r="R46" s="280"/>
-      <c r="S46" s="280"/>
-      <c r="T46" s="280"/>
-      <c r="U46" s="280"/>
-      <c r="V46" s="319"/>
-      <c r="W46" s="320"/>
+      <c r="N46" s="177"/>
+      <c r="O46" s="177"/>
+      <c r="P46" s="177"/>
+      <c r="Q46" s="177"/>
+      <c r="R46" s="177"/>
+      <c r="S46" s="177"/>
+      <c r="T46" s="177"/>
+      <c r="U46" s="177"/>
+      <c r="V46" s="278"/>
+      <c r="W46" s="279"/>
     </row>
     <row r="47" spans="2:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="81"/>
-      <c r="I47" s="81"/>
-      <c r="J47" s="81"/>
-      <c r="K47" s="81"/>
-      <c r="L47" s="81"/>
-      <c r="M47" s="224" t="s">
+      <c r="F47" s="54"/>
+      <c r="G47" s="55"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="76"/>
+      <c r="J47" s="76"/>
+      <c r="K47" s="76"/>
+      <c r="L47" s="76"/>
+      <c r="M47" s="245" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="224"/>
-      <c r="O47" s="224"/>
-      <c r="P47" s="224"/>
-      <c r="Q47" s="224"/>
-      <c r="R47" s="224"/>
-      <c r="S47" s="224"/>
-      <c r="T47" s="224"/>
-      <c r="U47" s="224"/>
-      <c r="V47" s="224"/>
-      <c r="W47" s="224"/>
+      <c r="N47" s="245"/>
+      <c r="O47" s="245"/>
+      <c r="P47" s="245"/>
+      <c r="Q47" s="245"/>
+      <c r="R47" s="245"/>
+      <c r="S47" s="245"/>
+      <c r="T47" s="245"/>
+      <c r="U47" s="245"/>
+      <c r="V47" s="245"/>
+      <c r="W47" s="245"/>
     </row>
     <row r="48" spans="2:25" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="81"/>
-      <c r="I48" s="81"/>
-      <c r="J48" s="81"/>
-      <c r="K48" s="81"/>
-      <c r="L48" s="81"/>
-      <c r="M48" s="225"/>
-      <c r="N48" s="225"/>
-      <c r="O48" s="225"/>
-      <c r="P48" s="225"/>
-      <c r="Q48" s="225"/>
-      <c r="R48" s="225"/>
-      <c r="S48" s="225"/>
-      <c r="T48" s="225"/>
-      <c r="U48" s="225"/>
-      <c r="V48" s="225"/>
-      <c r="W48" s="225"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="55"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="76"/>
+      <c r="K48" s="76"/>
+      <c r="L48" s="76"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="246"/>
+      <c r="O48" s="246"/>
+      <c r="P48" s="246"/>
+      <c r="Q48" s="246"/>
+      <c r="R48" s="246"/>
+      <c r="S48" s="246"/>
+      <c r="T48" s="246"/>
+      <c r="U48" s="246"/>
+      <c r="V48" s="246"/>
+      <c r="W48" s="246"/>
     </row>
     <row r="49" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="81"/>
-      <c r="I49" s="81"/>
-      <c r="J49" s="81"/>
-      <c r="K49" s="75"/>
-      <c r="L49" s="75"/>
-      <c r="M49" s="219" t="s">
+      <c r="F49" s="54"/>
+      <c r="G49" s="55"/>
+      <c r="H49" s="76"/>
+      <c r="I49" s="76"/>
+      <c r="J49" s="76"/>
+      <c r="K49" s="70"/>
+      <c r="L49" s="70"/>
+      <c r="M49" s="240" t="s">
         <v>17</v>
       </c>
-      <c r="N49" s="220"/>
-      <c r="O49" s="220"/>
-      <c r="P49" s="220"/>
-      <c r="Q49" s="220"/>
-      <c r="R49" s="178"/>
-      <c r="S49" s="178"/>
-      <c r="T49" s="223"/>
-      <c r="U49" s="223"/>
-      <c r="V49" s="311"/>
-      <c r="W49" s="312"/>
+      <c r="N49" s="241"/>
+      <c r="O49" s="241"/>
+      <c r="P49" s="241"/>
+      <c r="Q49" s="241"/>
+      <c r="R49" s="303"/>
+      <c r="S49" s="303"/>
+      <c r="T49" s="244"/>
+      <c r="U49" s="244"/>
+      <c r="V49" s="142"/>
+      <c r="W49" s="143"/>
     </row>
     <row r="50" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="88"/>
-      <c r="I50" s="88"/>
-      <c r="J50" s="88"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="55"/>
+      <c r="H50" s="83"/>
+      <c r="I50" s="83"/>
+      <c r="J50" s="83"/>
       <c r="K50" s="19"/>
-      <c r="L50" s="75"/>
-      <c r="M50" s="197" t="s">
+      <c r="L50" s="70"/>
+      <c r="M50" s="230" t="s">
         <v>18</v>
       </c>
-      <c r="N50" s="198"/>
-      <c r="O50" s="198"/>
-      <c r="P50" s="198"/>
-      <c r="Q50" s="198"/>
-      <c r="R50" s="321"/>
-      <c r="S50" s="321"/>
-      <c r="T50" s="226"/>
-      <c r="U50" s="226"/>
-      <c r="V50" s="217"/>
-      <c r="W50" s="218"/>
+      <c r="N50" s="231"/>
+      <c r="O50" s="231"/>
+      <c r="P50" s="231"/>
+      <c r="Q50" s="231"/>
+      <c r="R50" s="271"/>
+      <c r="S50" s="271"/>
+      <c r="T50" s="247"/>
+      <c r="U50" s="247"/>
+      <c r="V50" s="238"/>
+      <c r="W50" s="239"/>
     </row>
     <row r="51" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="89"/>
-      <c r="I51" s="89"/>
-      <c r="J51" s="89"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="55"/>
+      <c r="H51" s="84"/>
+      <c r="I51" s="84"/>
+      <c r="J51" s="84"/>
       <c r="K51" s="19"/>
-      <c r="L51" s="75"/>
-      <c r="M51" s="197" t="s">
+      <c r="L51" s="70"/>
+      <c r="M51" s="230" t="s">
         <v>10</v>
       </c>
-      <c r="N51" s="198"/>
-      <c r="O51" s="198"/>
-      <c r="P51" s="198"/>
-      <c r="Q51" s="198"/>
-      <c r="R51" s="199"/>
-      <c r="S51" s="199"/>
-      <c r="T51" s="200"/>
-      <c r="U51" s="200"/>
-      <c r="V51" s="181"/>
-      <c r="W51" s="182"/>
+      <c r="N51" s="231"/>
+      <c r="O51" s="231"/>
+      <c r="P51" s="231"/>
+      <c r="Q51" s="231"/>
+      <c r="R51" s="273"/>
+      <c r="S51" s="273"/>
+      <c r="T51" s="274"/>
+      <c r="U51" s="274"/>
+      <c r="V51" s="140"/>
+      <c r="W51" s="141"/>
     </row>
     <row r="52" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="58"/>
-      <c r="H52" s="90"/>
-      <c r="I52" s="91"/>
-      <c r="J52" s="75"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="85"/>
+      <c r="I52" s="86"/>
+      <c r="J52" s="70"/>
       <c r="K52" s="19"/>
       <c r="L52" s="18"/>
-      <c r="M52" s="197" t="s">
+      <c r="M52" s="230" t="s">
         <v>19</v>
       </c>
-      <c r="N52" s="198"/>
-      <c r="O52" s="198"/>
-      <c r="P52" s="198"/>
-      <c r="Q52" s="198"/>
-      <c r="R52" s="201"/>
-      <c r="S52" s="201"/>
-      <c r="T52" s="196"/>
-      <c r="U52" s="196"/>
-      <c r="V52" s="181"/>
-      <c r="W52" s="182"/>
+      <c r="N52" s="231"/>
+      <c r="O52" s="231"/>
+      <c r="P52" s="231"/>
+      <c r="Q52" s="231"/>
+      <c r="R52" s="275"/>
+      <c r="S52" s="275"/>
+      <c r="T52" s="272"/>
+      <c r="U52" s="272"/>
+      <c r="V52" s="140"/>
+      <c r="W52" s="141"/>
     </row>
     <row r="53" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="81"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="92"/>
-      <c r="K53" s="92"/>
-      <c r="L53" s="92"/>
-      <c r="M53" s="179" t="s">
+      <c r="F53" s="54"/>
+      <c r="G53" s="55"/>
+      <c r="H53" s="76"/>
+      <c r="I53" s="76"/>
+      <c r="J53" s="87"/>
+      <c r="K53" s="87"/>
+      <c r="L53" s="87"/>
+      <c r="M53" s="216" t="s">
         <v>26</v>
       </c>
-      <c r="N53" s="180"/>
-      <c r="O53" s="180"/>
-      <c r="P53" s="180"/>
-      <c r="Q53" s="180"/>
-      <c r="R53" s="202"/>
-      <c r="S53" s="202"/>
-      <c r="T53" s="143" t="s">
+      <c r="N53" s="217"/>
+      <c r="O53" s="217"/>
+      <c r="P53" s="217"/>
+      <c r="Q53" s="217"/>
+      <c r="R53" s="277"/>
+      <c r="S53" s="277"/>
+      <c r="T53" s="276" t="s">
         <v>25</v>
       </c>
-      <c r="U53" s="143"/>
-      <c r="V53" s="144"/>
-      <c r="W53" s="145"/>
+      <c r="U53" s="276"/>
+      <c r="V53" s="280"/>
+      <c r="W53" s="281"/>
     </row>
     <row r="54" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-      <c r="F54" s="57"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="81"/>
-      <c r="I54" s="81"/>
-      <c r="J54" s="142"/>
-      <c r="K54" s="142"/>
-      <c r="L54" s="142"/>
-      <c r="M54" s="179" t="s">
+      <c r="F54" s="54"/>
+      <c r="G54" s="55"/>
+      <c r="H54" s="76"/>
+      <c r="I54" s="76"/>
+      <c r="J54" s="137"/>
+      <c r="K54" s="137"/>
+      <c r="L54" s="137"/>
+      <c r="M54" s="216" t="s">
         <v>65</v>
       </c>
-      <c r="N54" s="180"/>
-      <c r="O54" s="180"/>
-      <c r="P54" s="180"/>
-      <c r="Q54" s="180"/>
-      <c r="R54" s="202"/>
-      <c r="S54" s="202"/>
-      <c r="T54" s="143"/>
-      <c r="U54" s="143"/>
-      <c r="V54" s="144"/>
-      <c r="W54" s="145"/>
+      <c r="N54" s="217"/>
+      <c r="O54" s="217"/>
+      <c r="P54" s="217"/>
+      <c r="Q54" s="217"/>
+      <c r="R54" s="277"/>
+      <c r="S54" s="277"/>
+      <c r="T54" s="276"/>
+      <c r="U54" s="276"/>
+      <c r="V54" s="280"/>
+      <c r="W54" s="281"/>
     </row>
     <row r="55" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="57"/>
-      <c r="G55" s="58"/>
-      <c r="H55" s="89"/>
-      <c r="I55" s="89"/>
-      <c r="J55" s="89"/>
-      <c r="L55" s="93"/>
-      <c r="M55" s="179" t="s">
+      <c r="F55" s="54"/>
+      <c r="G55" s="55"/>
+      <c r="H55" s="84"/>
+      <c r="I55" s="84"/>
+      <c r="J55" s="84"/>
+      <c r="L55" s="88"/>
+      <c r="M55" s="216" t="s">
         <v>20</v>
       </c>
-      <c r="N55" s="180"/>
-      <c r="O55" s="180"/>
-      <c r="P55" s="180"/>
-      <c r="Q55" s="180"/>
-      <c r="R55" s="238"/>
-      <c r="S55" s="238"/>
-      <c r="T55" s="208"/>
-      <c r="U55" s="208"/>
-      <c r="V55" s="183"/>
-      <c r="W55" s="184"/>
+      <c r="N55" s="217"/>
+      <c r="O55" s="217"/>
+      <c r="P55" s="217"/>
+      <c r="Q55" s="217"/>
+      <c r="R55" s="233"/>
+      <c r="S55" s="233"/>
+      <c r="T55" s="263"/>
+      <c r="U55" s="263"/>
+      <c r="V55" s="282"/>
+      <c r="W55" s="283"/>
     </row>
     <row r="56" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
-      <c r="F56" s="57"/>
-      <c r="G56" s="58"/>
-      <c r="H56" s="88"/>
-      <c r="I56" s="88"/>
-      <c r="J56" s="88"/>
-      <c r="K56" s="94"/>
-      <c r="L56" s="86"/>
-      <c r="M56" s="197" t="s">
+      <c r="F56" s="54"/>
+      <c r="G56" s="55"/>
+      <c r="H56" s="83"/>
+      <c r="I56" s="83"/>
+      <c r="J56" s="83"/>
+      <c r="K56" s="89"/>
+      <c r="L56" s="81"/>
+      <c r="M56" s="230" t="s">
         <v>21</v>
       </c>
-      <c r="N56" s="198"/>
-      <c r="O56" s="198"/>
-      <c r="P56" s="198"/>
-      <c r="Q56" s="198"/>
-      <c r="R56" s="195"/>
-      <c r="S56" s="195"/>
-      <c r="T56" s="196" t="s">
+      <c r="N56" s="231"/>
+      <c r="O56" s="231"/>
+      <c r="P56" s="231"/>
+      <c r="Q56" s="231"/>
+      <c r="R56" s="270"/>
+      <c r="S56" s="270"/>
+      <c r="T56" s="272" t="s">
         <v>7</v>
       </c>
-      <c r="U56" s="196"/>
-      <c r="V56" s="209"/>
-      <c r="W56" s="210"/>
+      <c r="U56" s="272"/>
+      <c r="V56" s="264"/>
+      <c r="W56" s="265"/>
     </row>
     <row r="57" spans="2:23" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
-      <c r="F57" s="57"/>
-      <c r="G57" s="58"/>
-      <c r="H57" s="85"/>
-      <c r="I57" s="85"/>
-      <c r="J57" s="85"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="55"/>
+      <c r="H57" s="80"/>
+      <c r="I57" s="80"/>
+      <c r="J57" s="80"/>
       <c r="K57" s="18"/>
-      <c r="L57" s="95"/>
-      <c r="M57" s="197" t="s">
+      <c r="L57" s="90"/>
+      <c r="M57" s="230" t="s">
         <v>39</v>
       </c>
-      <c r="N57" s="198"/>
-      <c r="O57" s="198"/>
-      <c r="P57" s="198"/>
-      <c r="Q57" s="198"/>
-      <c r="R57" s="205"/>
-      <c r="S57" s="206"/>
-      <c r="T57" s="206"/>
-      <c r="U57" s="206"/>
-      <c r="V57" s="206"/>
-      <c r="W57" s="207"/>
+      <c r="N57" s="231"/>
+      <c r="O57" s="231"/>
+      <c r="P57" s="231"/>
+      <c r="Q57" s="231"/>
+      <c r="R57" s="314"/>
+      <c r="S57" s="315"/>
+      <c r="T57" s="315"/>
+      <c r="U57" s="315"/>
+      <c r="V57" s="315"/>
+      <c r="W57" s="316"/>
     </row>
     <row r="58" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
-      <c r="F58" s="57"/>
-      <c r="G58" s="58"/>
-      <c r="H58" s="75"/>
-      <c r="I58" s="96"/>
-      <c r="J58" s="96"/>
-      <c r="K58" s="75"/>
-      <c r="L58" s="97"/>
-      <c r="M58" s="179" t="s">
+      <c r="F58" s="54"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="70"/>
+      <c r="I58" s="91"/>
+      <c r="J58" s="91"/>
+      <c r="K58" s="70"/>
+      <c r="L58" s="92"/>
+      <c r="M58" s="216" t="s">
         <v>44</v>
       </c>
-      <c r="N58" s="180"/>
-      <c r="O58" s="180"/>
-      <c r="P58" s="180"/>
-      <c r="Q58" s="180"/>
-      <c r="R58" s="211"/>
-      <c r="S58" s="211"/>
-      <c r="T58" s="215"/>
-      <c r="U58" s="215"/>
-      <c r="V58" s="215"/>
-      <c r="W58" s="228"/>
+      <c r="N58" s="217"/>
+      <c r="O58" s="217"/>
+      <c r="P58" s="217"/>
+      <c r="Q58" s="217"/>
+      <c r="R58" s="232"/>
+      <c r="S58" s="232"/>
+      <c r="T58" s="249"/>
+      <c r="U58" s="249"/>
+      <c r="V58" s="249"/>
+      <c r="W58" s="250"/>
     </row>
     <row r="59" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
-      <c r="F59" s="57"/>
-      <c r="G59" s="58"/>
-      <c r="H59" s="75"/>
-      <c r="I59" s="86"/>
-      <c r="J59" s="75"/>
-      <c r="K59" s="75"/>
-      <c r="L59" s="98"/>
-      <c r="M59" s="179" t="s">
+      <c r="F59" s="54"/>
+      <c r="G59" s="55"/>
+      <c r="H59" s="70"/>
+      <c r="I59" s="81"/>
+      <c r="J59" s="70"/>
+      <c r="K59" s="70"/>
+      <c r="L59" s="93"/>
+      <c r="M59" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="N59" s="180"/>
-      <c r="O59" s="180"/>
-      <c r="P59" s="180"/>
-      <c r="Q59" s="180"/>
-      <c r="R59" s="211"/>
-      <c r="S59" s="211"/>
-      <c r="T59" s="216"/>
-      <c r="U59" s="216"/>
-      <c r="V59" s="215"/>
-      <c r="W59" s="228"/>
+      <c r="N59" s="217"/>
+      <c r="O59" s="217"/>
+      <c r="P59" s="217"/>
+      <c r="Q59" s="217"/>
+      <c r="R59" s="232"/>
+      <c r="S59" s="232"/>
+      <c r="T59" s="269"/>
+      <c r="U59" s="269"/>
+      <c r="V59" s="249"/>
+      <c r="W59" s="250"/>
     </row>
     <row r="60" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
-      <c r="F60" s="57"/>
-      <c r="G60" s="58"/>
-      <c r="H60" s="99"/>
-      <c r="I60" s="76"/>
-      <c r="J60" s="76"/>
-      <c r="K60" s="76"/>
-      <c r="L60" s="76"/>
-      <c r="M60" s="179" t="s">
+      <c r="F60" s="54"/>
+      <c r="G60" s="55"/>
+      <c r="H60" s="94"/>
+      <c r="I60" s="71"/>
+      <c r="J60" s="71"/>
+      <c r="K60" s="71"/>
+      <c r="L60" s="71"/>
+      <c r="M60" s="216" t="s">
         <v>9</v>
       </c>
-      <c r="N60" s="180"/>
-      <c r="O60" s="180"/>
-      <c r="P60" s="180"/>
-      <c r="Q60" s="180"/>
-      <c r="R60" s="233"/>
-      <c r="S60" s="233"/>
-      <c r="T60" s="211" t="s">
+      <c r="N60" s="217"/>
+      <c r="O60" s="217"/>
+      <c r="P60" s="217"/>
+      <c r="Q60" s="217"/>
+      <c r="R60" s="255"/>
+      <c r="S60" s="255"/>
+      <c r="T60" s="232" t="s">
         <v>0</v>
       </c>
-      <c r="U60" s="211"/>
-      <c r="V60" s="229"/>
-      <c r="W60" s="230"/>
+      <c r="U60" s="232"/>
+      <c r="V60" s="251"/>
+      <c r="W60" s="252"/>
     </row>
     <row r="61" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="58"/>
-      <c r="H61" s="75"/>
-      <c r="I61" s="100"/>
-      <c r="J61" s="100"/>
-      <c r="K61" s="100"/>
-      <c r="L61" s="100"/>
-      <c r="M61" s="197" t="s">
+      <c r="F61" s="54"/>
+      <c r="G61" s="55"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="95"/>
+      <c r="J61" s="95"/>
+      <c r="K61" s="95"/>
+      <c r="L61" s="95"/>
+      <c r="M61" s="230" t="s">
         <v>42</v>
       </c>
-      <c r="N61" s="198"/>
-      <c r="O61" s="198"/>
-      <c r="P61" s="198"/>
-      <c r="Q61" s="198"/>
-      <c r="R61" s="174"/>
-      <c r="S61" s="174"/>
-      <c r="T61" s="211"/>
-      <c r="U61" s="211"/>
-      <c r="V61" s="176"/>
-      <c r="W61" s="177"/>
+      <c r="N61" s="231"/>
+      <c r="O61" s="231"/>
+      <c r="P61" s="231"/>
+      <c r="Q61" s="231"/>
+      <c r="R61" s="260"/>
+      <c r="S61" s="260"/>
+      <c r="T61" s="232"/>
+      <c r="U61" s="232"/>
+      <c r="V61" s="258"/>
+      <c r="W61" s="259"/>
     </row>
     <row r="62" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
-      <c r="F62" s="57"/>
-      <c r="G62" s="58"/>
-      <c r="H62" s="75"/>
-      <c r="I62" s="100"/>
-      <c r="J62" s="100"/>
-      <c r="K62" s="100"/>
-      <c r="L62" s="100"/>
-      <c r="M62" s="197" t="s">
+      <c r="F62" s="54"/>
+      <c r="G62" s="55"/>
+      <c r="H62" s="70"/>
+      <c r="I62" s="95"/>
+      <c r="J62" s="95"/>
+      <c r="K62" s="95"/>
+      <c r="L62" s="95"/>
+      <c r="M62" s="230" t="s">
         <v>47</v>
       </c>
-      <c r="N62" s="198"/>
-      <c r="O62" s="198"/>
-      <c r="P62" s="198"/>
-      <c r="Q62" s="198"/>
-      <c r="R62" s="174"/>
-      <c r="S62" s="174"/>
-      <c r="T62" s="211"/>
-      <c r="U62" s="211"/>
-      <c r="V62" s="176"/>
-      <c r="W62" s="177"/>
+      <c r="N62" s="231"/>
+      <c r="O62" s="231"/>
+      <c r="P62" s="231"/>
+      <c r="Q62" s="231"/>
+      <c r="R62" s="260"/>
+      <c r="S62" s="260"/>
+      <c r="T62" s="232"/>
+      <c r="U62" s="232"/>
+      <c r="V62" s="258"/>
+      <c r="W62" s="259"/>
     </row>
     <row r="63" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="11"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
-      <c r="F63" s="57"/>
-      <c r="G63" s="58"/>
-      <c r="H63" s="75"/>
-      <c r="I63" s="227" t="s">
+      <c r="F63" s="54"/>
+      <c r="G63" s="55"/>
+      <c r="H63" s="70"/>
+      <c r="I63" s="248" t="s">
         <v>48</v>
       </c>
-      <c r="J63" s="227"/>
-      <c r="K63" s="227"/>
-      <c r="L63" s="227"/>
-      <c r="M63" s="197" t="s">
+      <c r="J63" s="248"/>
+      <c r="K63" s="248"/>
+      <c r="L63" s="248"/>
+      <c r="M63" s="230" t="s">
         <v>24</v>
       </c>
-      <c r="N63" s="198"/>
-      <c r="O63" s="198"/>
-      <c r="P63" s="198"/>
-      <c r="Q63" s="198"/>
-      <c r="R63" s="175"/>
-      <c r="S63" s="175"/>
-      <c r="T63" s="234"/>
-      <c r="U63" s="234"/>
-      <c r="V63" s="231"/>
-      <c r="W63" s="232"/>
+      <c r="N63" s="231"/>
+      <c r="O63" s="231"/>
+      <c r="P63" s="231"/>
+      <c r="Q63" s="231"/>
+      <c r="R63" s="302"/>
+      <c r="S63" s="302"/>
+      <c r="T63" s="256"/>
+      <c r="U63" s="256"/>
+      <c r="V63" s="253"/>
+      <c r="W63" s="254"/>
     </row>
     <row r="64" spans="2:23" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B64" s="11"/>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
       <c r="E64" s="3"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="60"/>
-      <c r="H64" s="75"/>
-      <c r="I64" s="165"/>
-      <c r="J64" s="165"/>
-      <c r="K64" s="165"/>
-      <c r="L64" s="166"/>
-      <c r="M64" s="236" t="s">
+      <c r="F64" s="56"/>
+      <c r="G64" s="57"/>
+      <c r="H64" s="70"/>
+      <c r="I64" s="178"/>
+      <c r="J64" s="178"/>
+      <c r="K64" s="178"/>
+      <c r="L64" s="179"/>
+      <c r="M64" s="261" t="s">
         <v>23</v>
       </c>
-      <c r="N64" s="237"/>
-      <c r="O64" s="237"/>
-      <c r="P64" s="237"/>
-      <c r="Q64" s="237"/>
-      <c r="R64" s="212"/>
-      <c r="S64" s="212"/>
-      <c r="T64" s="235"/>
-      <c r="U64" s="235"/>
-      <c r="V64" s="213"/>
-      <c r="W64" s="214"/>
+      <c r="N64" s="262"/>
+      <c r="O64" s="262"/>
+      <c r="P64" s="262"/>
+      <c r="Q64" s="262"/>
+      <c r="R64" s="266"/>
+      <c r="S64" s="266"/>
+      <c r="T64" s="257"/>
+      <c r="U64" s="257"/>
+      <c r="V64" s="267"/>
+      <c r="W64" s="268"/>
     </row>
     <row r="65" spans="2:23" s="6" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B65" s="11"/>
@@ -5929,153 +5929,347 @@
       <c r="H65" s="8"/>
       <c r="I65" s="7"/>
       <c r="J65" s="7"/>
-      <c r="M65" s="48" t="s">
+      <c r="M65" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="N65" s="49"/>
-      <c r="O65" s="48"/>
-      <c r="P65" s="48"/>
-      <c r="Q65" s="48"/>
-      <c r="R65" s="48"/>
-      <c r="S65" s="48"/>
-      <c r="T65" s="48"/>
-      <c r="U65" s="48"/>
+      <c r="N65" s="46"/>
+      <c r="O65" s="45"/>
+      <c r="P65" s="45"/>
+      <c r="Q65" s="45"/>
+      <c r="R65" s="45"/>
+      <c r="S65" s="45"/>
+      <c r="T65" s="45"/>
+      <c r="U65" s="45"/>
       <c r="V65" s="16"/>
       <c r="W65" s="16"/>
     </row>
     <row r="66" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L66" s="146" t="s">
+      <c r="L66" s="295" t="s">
         <v>49</v>
       </c>
-      <c r="M66" s="147"/>
-      <c r="N66" s="147"/>
-      <c r="O66" s="147"/>
-      <c r="P66" s="147"/>
-      <c r="Q66" s="147"/>
-      <c r="R66" s="147"/>
-      <c r="S66" s="147"/>
-      <c r="T66" s="147"/>
-      <c r="U66" s="147"/>
-      <c r="V66" s="147"/>
-      <c r="W66" s="156"/>
+      <c r="M66" s="296"/>
+      <c r="N66" s="296"/>
+      <c r="O66" s="296"/>
+      <c r="P66" s="296"/>
+      <c r="Q66" s="296"/>
+      <c r="R66" s="296"/>
+      <c r="S66" s="296"/>
+      <c r="T66" s="296"/>
+      <c r="U66" s="296"/>
+      <c r="V66" s="296"/>
+      <c r="W66" s="297"/>
     </row>
     <row r="67" spans="2:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L67" s="152" t="s">
+      <c r="L67" s="307" t="s">
         <v>50</v>
       </c>
-      <c r="M67" s="150" t="s">
+      <c r="M67" s="284" t="s">
         <v>27</v>
       </c>
-      <c r="N67" s="150" t="s">
+      <c r="N67" s="284" t="s">
         <v>28</v>
       </c>
-      <c r="O67" s="150" t="s">
+      <c r="O67" s="284" t="s">
         <v>29</v>
       </c>
-      <c r="P67" s="150" t="s">
+      <c r="P67" s="284" t="s">
         <v>31</v>
       </c>
-      <c r="Q67" s="150"/>
-      <c r="R67" s="150"/>
-      <c r="S67" s="150"/>
-      <c r="T67" s="150" t="s">
+      <c r="Q67" s="284"/>
+      <c r="R67" s="284"/>
+      <c r="S67" s="284"/>
+      <c r="T67" s="284" t="s">
         <v>51</v>
       </c>
-      <c r="U67" s="150"/>
-      <c r="V67" s="150" t="s">
+      <c r="U67" s="284"/>
+      <c r="V67" s="284" t="s">
         <v>52</v>
       </c>
-      <c r="W67" s="160"/>
+      <c r="W67" s="285"/>
     </row>
     <row r="68" spans="2:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L68" s="152"/>
-      <c r="M68" s="150"/>
-      <c r="N68" s="150"/>
-      <c r="O68" s="150"/>
-      <c r="P68" s="151" t="s">
+      <c r="L68" s="307"/>
+      <c r="M68" s="284"/>
+      <c r="N68" s="284"/>
+      <c r="O68" s="284"/>
+      <c r="P68" s="306" t="s">
         <v>33</v>
       </c>
-      <c r="Q68" s="151"/>
-      <c r="R68" s="150" t="s">
+      <c r="Q68" s="306"/>
+      <c r="R68" s="284" t="s">
         <v>13</v>
       </c>
-      <c r="S68" s="150"/>
-      <c r="T68" s="150" t="s">
+      <c r="S68" s="284"/>
+      <c r="T68" s="284" t="s">
         <v>57</v>
       </c>
-      <c r="U68" s="150"/>
-      <c r="V68" s="150" t="s">
+      <c r="U68" s="284"/>
+      <c r="V68" s="284" t="s">
         <v>58</v>
       </c>
-      <c r="W68" s="160"/>
+      <c r="W68" s="285"/>
     </row>
     <row r="69" spans="2:23" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="L69" s="53"/>
-      <c r="M69" s="54"/>
-      <c r="N69" s="54"/>
-      <c r="O69" s="52"/>
-      <c r="P69" s="157"/>
-      <c r="Q69" s="157"/>
-      <c r="R69" s="157"/>
-      <c r="S69" s="157"/>
-      <c r="T69" s="157"/>
-      <c r="U69" s="157"/>
-      <c r="V69" s="157"/>
-      <c r="W69" s="203"/>
+      <c r="L69" s="50"/>
+      <c r="M69" s="51"/>
+      <c r="N69" s="51"/>
+      <c r="O69" s="49"/>
+      <c r="P69" s="311"/>
+      <c r="Q69" s="311"/>
+      <c r="R69" s="311"/>
+      <c r="S69" s="311"/>
+      <c r="T69" s="311"/>
+      <c r="U69" s="311"/>
+      <c r="V69" s="311"/>
+      <c r="W69" s="312"/>
     </row>
     <row r="70" spans="2:23" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="L70" s="46"/>
-      <c r="M70" s="46"/>
-      <c r="N70" s="204"/>
-      <c r="O70" s="204"/>
-      <c r="P70" s="204"/>
-      <c r="Q70" s="204"/>
-      <c r="R70" s="46"/>
-      <c r="S70" s="46"/>
-      <c r="T70" s="46"/>
-      <c r="U70" s="46"/>
-      <c r="V70" s="46"/>
-      <c r="W70" s="46"/>
+      <c r="L70" s="43"/>
+      <c r="M70" s="43"/>
+      <c r="N70" s="313"/>
+      <c r="O70" s="313"/>
+      <c r="P70" s="313"/>
+      <c r="Q70" s="313"/>
+      <c r="R70" s="43"/>
+      <c r="S70" s="43"/>
+      <c r="T70" s="43"/>
+      <c r="U70" s="43"/>
+      <c r="V70" s="43"/>
+      <c r="W70" s="43"/>
     </row>
     <row r="71" spans="2:23" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L71" s="146" t="s">
+      <c r="L71" s="295" t="s">
         <v>53</v>
       </c>
-      <c r="M71" s="147"/>
-      <c r="N71" s="147" t="s">
+      <c r="M71" s="296"/>
+      <c r="N71" s="296" t="s">
         <v>54</v>
       </c>
-      <c r="O71" s="147"/>
-      <c r="P71" s="147" t="s">
+      <c r="O71" s="296"/>
+      <c r="P71" s="296" t="s">
         <v>55</v>
       </c>
-      <c r="Q71" s="156"/>
-      <c r="R71" s="153"/>
-      <c r="S71" s="153"/>
-      <c r="T71" s="46"/>
-      <c r="U71" s="46"/>
-      <c r="V71" s="46"/>
-      <c r="W71" s="46"/>
+      <c r="Q71" s="297"/>
+      <c r="R71" s="308"/>
+      <c r="S71" s="308"/>
+      <c r="T71" s="43"/>
+      <c r="U71" s="43"/>
+      <c r="V71" s="43"/>
+      <c r="W71" s="43"/>
     </row>
     <row r="72" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="L72" s="148"/>
-      <c r="M72" s="149"/>
-      <c r="N72" s="149"/>
-      <c r="O72" s="149"/>
-      <c r="P72" s="149"/>
-      <c r="Q72" s="154"/>
-      <c r="R72" s="155"/>
-      <c r="S72" s="155"/>
-      <c r="T72" s="46"/>
-      <c r="U72" s="46"/>
-      <c r="V72" s="46"/>
-      <c r="W72" s="46"/>
+      <c r="L72" s="304"/>
+      <c r="M72" s="305"/>
+      <c r="N72" s="305"/>
+      <c r="O72" s="305"/>
+      <c r="P72" s="305"/>
+      <c r="Q72" s="309"/>
+      <c r="R72" s="310"/>
+      <c r="S72" s="310"/>
+      <c r="T72" s="43"/>
+      <c r="U72" s="43"/>
+      <c r="V72" s="43"/>
+      <c r="W72" s="43"/>
     </row>
     <row r="117" ht="65.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="118" ht="65.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="119" ht="65.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="218">
+    <mergeCell ref="T54:U54"/>
+    <mergeCell ref="V54:W54"/>
+    <mergeCell ref="L71:M71"/>
+    <mergeCell ref="L72:M72"/>
+    <mergeCell ref="P67:S67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="L67:L68"/>
+    <mergeCell ref="M67:M68"/>
+    <mergeCell ref="N67:N68"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="N72:O72"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="N71:O71"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="T69:U69"/>
+    <mergeCell ref="V69:W69"/>
+    <mergeCell ref="N70:O70"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="O67:O68"/>
+    <mergeCell ref="R57:W57"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="L66:W66"/>
+    <mergeCell ref="T68:U68"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="V25:V26"/>
+    <mergeCell ref="W25:W26"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="S41:T41"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="J38:L38"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="S37:T37"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="R61:S61"/>
+    <mergeCell ref="R63:S63"/>
+    <mergeCell ref="V61:W61"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="V46:W46"/>
+    <mergeCell ref="M55:Q55"/>
+    <mergeCell ref="M53:Q53"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="V53:W53"/>
+    <mergeCell ref="V55:W55"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="V67:W67"/>
+    <mergeCell ref="V14:V17"/>
+    <mergeCell ref="W14:W17"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="S31:T31"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="S36:T36"/>
+    <mergeCell ref="R56:S56"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="T56:U56"/>
+    <mergeCell ref="M51:Q51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="T51:U51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="T53:U53"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="M54:Q54"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="T55:U55"/>
+    <mergeCell ref="V56:W56"/>
+    <mergeCell ref="M58:Q58"/>
+    <mergeCell ref="M59:Q59"/>
+    <mergeCell ref="T60:U60"/>
+    <mergeCell ref="R64:S64"/>
+    <mergeCell ref="V64:W64"/>
+    <mergeCell ref="T58:U58"/>
+    <mergeCell ref="T59:U59"/>
+    <mergeCell ref="V50:W50"/>
+    <mergeCell ref="M49:Q49"/>
+    <mergeCell ref="M50:Q50"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="M47:W48"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="I64:L64"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="V58:W58"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="V60:W60"/>
+    <mergeCell ref="V63:W63"/>
+    <mergeCell ref="R60:S60"/>
+    <mergeCell ref="T61:U61"/>
+    <mergeCell ref="T63:U63"/>
+    <mergeCell ref="T64:U64"/>
+    <mergeCell ref="V62:W62"/>
+    <mergeCell ref="R62:S62"/>
+    <mergeCell ref="T62:U62"/>
+    <mergeCell ref="M62:Q62"/>
+    <mergeCell ref="M64:Q64"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="M61:Q61"/>
+    <mergeCell ref="M63:Q63"/>
+    <mergeCell ref="R58:S58"/>
+    <mergeCell ref="M60:Q60"/>
+    <mergeCell ref="M52:Q52"/>
+    <mergeCell ref="M56:Q56"/>
+    <mergeCell ref="M57:Q57"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="S39:T39"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J31:L31"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="M4:W5"/>
+    <mergeCell ref="P7:W7"/>
+    <mergeCell ref="P8:W8"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="P6:W6"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="S9:T10"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="R9:R10"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B3:U3"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="U14:U17"/>
+    <mergeCell ref="M14:O17"/>
+    <mergeCell ref="P14:P17"/>
+    <mergeCell ref="D6:E12"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="M46:U46"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="O25:P26"/>
+    <mergeCell ref="M42:W43"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="M25:N26"/>
+    <mergeCell ref="Q14:Q17"/>
+    <mergeCell ref="R14:R17"/>
+    <mergeCell ref="S14:S17"/>
+    <mergeCell ref="T14:T17"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M22:O22"/>
     <mergeCell ref="S19:T19"/>
     <mergeCell ref="V51:W51"/>
     <mergeCell ref="V49:W49"/>
@@ -6100,200 +6294,6 @@
     <mergeCell ref="S29:T29"/>
     <mergeCell ref="M30:N30"/>
     <mergeCell ref="S28:T28"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="U14:U17"/>
-    <mergeCell ref="M14:O17"/>
-    <mergeCell ref="P14:P17"/>
-    <mergeCell ref="D6:E12"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="M46:U46"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="O25:P26"/>
-    <mergeCell ref="M42:W43"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="M25:N26"/>
-    <mergeCell ref="Q14:Q17"/>
-    <mergeCell ref="R14:R17"/>
-    <mergeCell ref="S14:S17"/>
-    <mergeCell ref="T14:T17"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="M4:W5"/>
-    <mergeCell ref="P7:W7"/>
-    <mergeCell ref="P8:W8"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="P6:W6"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="S9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="Q9:Q10"/>
-    <mergeCell ref="R9:R10"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B3:U3"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="M61:Q61"/>
-    <mergeCell ref="M63:Q63"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="M60:Q60"/>
-    <mergeCell ref="M52:Q52"/>
-    <mergeCell ref="M56:Q56"/>
-    <mergeCell ref="M57:Q57"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="S39:T39"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="S40:T40"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J31:L31"/>
-    <mergeCell ref="V50:W50"/>
-    <mergeCell ref="M49:Q49"/>
-    <mergeCell ref="M50:Q50"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="M47:W48"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="I64:L64"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="V58:W58"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="V60:W60"/>
-    <mergeCell ref="V63:W63"/>
-    <mergeCell ref="R60:S60"/>
-    <mergeCell ref="T61:U61"/>
-    <mergeCell ref="T63:U63"/>
-    <mergeCell ref="T64:U64"/>
-    <mergeCell ref="V62:W62"/>
-    <mergeCell ref="R62:S62"/>
-    <mergeCell ref="T62:U62"/>
-    <mergeCell ref="M62:Q62"/>
-    <mergeCell ref="M64:Q64"/>
-    <mergeCell ref="T55:U55"/>
-    <mergeCell ref="V56:W56"/>
-    <mergeCell ref="M58:Q58"/>
-    <mergeCell ref="M59:Q59"/>
-    <mergeCell ref="T60:U60"/>
-    <mergeCell ref="R64:S64"/>
-    <mergeCell ref="V64:W64"/>
-    <mergeCell ref="T58:U58"/>
-    <mergeCell ref="T59:U59"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S38:T38"/>
-    <mergeCell ref="S36:T36"/>
-    <mergeCell ref="R56:S56"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="T56:U56"/>
-    <mergeCell ref="M51:Q51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="T51:U51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="T53:U53"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="M54:Q54"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="V46:W46"/>
-    <mergeCell ref="M55:Q55"/>
-    <mergeCell ref="M53:Q53"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="V53:W53"/>
-    <mergeCell ref="V55:W55"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="V67:W67"/>
-    <mergeCell ref="V14:V17"/>
-    <mergeCell ref="W14:W17"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="S34:T34"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="S31:T31"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="L66:W66"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="V25:V26"/>
-    <mergeCell ref="W25:W26"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="S41:T41"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="J38:L38"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="S37:T37"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="R61:S61"/>
-    <mergeCell ref="R63:S63"/>
-    <mergeCell ref="V61:W61"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="T54:U54"/>
-    <mergeCell ref="V54:W54"/>
-    <mergeCell ref="L71:M71"/>
-    <mergeCell ref="L72:M72"/>
-    <mergeCell ref="P67:S67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="L67:L68"/>
-    <mergeCell ref="M67:M68"/>
-    <mergeCell ref="N67:N68"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="N72:O72"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="N71:O71"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="T69:U69"/>
-    <mergeCell ref="V69:W69"/>
-    <mergeCell ref="N70:O70"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="O67:O68"/>
-    <mergeCell ref="R57:W57"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0.11811023622047245" footer="0.19685039370078741"/>
